--- a/input_data/data/Proforma_Template.xlsx
+++ b/input_data/data/Proforma_Template.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -44,12 +44,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2E3E5"/>
         <bgColor rgb="00E2E3E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,9 +94,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -545,19 +536,47 @@
       <c r="N2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n"/>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>default_id</t>
+        </is>
+      </c>
       <c r="B3" s="3" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FP1</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="n"/>
-      <c r="K3" s="4" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="n"/>
     </row>
     <row r="5">
@@ -677,263 +696,271 @@
       <c r="A7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>MON</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>TUE</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>KRPUS01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>SUM(E7:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5">
-        <f>SUM(I7:I16)</f>
-        <v/>
-      </c>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5">
-        <f>SUM(M7:M16)</f>
-        <v/>
-      </c>
-      <c r="N17" s="5">
-        <f>SUM(N7:N16)</f>
-        <v/>
-      </c>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5">
-        <f>IF(Q17&gt;0, N17/Q17, 0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="5">
-        <f>SUM(Q7:Q16)</f>
-        <v/>
-      </c>
-      <c r="R17" s="5" t="n"/>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="14">
